--- a/erp-server/erp-server-dmp/src/main/resources/excel/adsErpFirstMileInTransitInit.xlsx
+++ b/erp-server/erp-server-dmp/src/main/resources/excel/adsErpFirstMileInTransitInit.xlsx
@@ -41,7 +41,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>月份</t>
+      <t>导入月份</t>
     </r>
   </si>
   <si>
@@ -70,6 +70,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
